--- a/output/mpbart_dgp2extranoise_output.xlsx
+++ b/output/mpbart_dgp2extranoise_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5cac48941448979/Bureaublad/msc_thesis/thesis_code/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED800B34FA19D842FAAD744173DEDE9E2BF74" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{394D3C61-BBE2-4F78-80D4-5E4ED795E4B8}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED800F1EF69EE9E9EB7FC243731EDE9E2BF73" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C7EA977-B9DD-4BC1-B4B6-2D58A3BF0491}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misclassification_rates" sheetId="1" r:id="rId1"/>
@@ -378,52 +378,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.32900000000000001</v>
+        <v>0.28399999999999997</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.34300000000000003</v>
+        <v>0.26600000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.32400000000000001</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.34499999999999997</v>
+        <v>0.27200000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.34200000000000003</v>
+        <v>0.29199999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.33800000000000002</v>
+        <v>0.27800000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.31900000000000001</v>
+        <v>0.26200000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.34300000000000003</v>
+        <v>0.29099999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.29299999999999998</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.32800000000000001</v>
+        <v>0.28100000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -432,7 +432,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.33039999999999997</v>
+        <v>0.27390000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -441,7 +441,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>1.5987495113369082E-2</v>
+        <v>1.3444949485463544E-2</v>
       </c>
     </row>
   </sheetData>
@@ -457,52 +457,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.42882411111111102</v>
+        <v>0.41255222755555598</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.44924714844444402</v>
+        <v>0.39127959466666701</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.44496349422222198</v>
+        <v>0.379472731555556</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.45194068266666698</v>
+        <v>0.37855588177777799</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.44271373244444401</v>
+        <v>0.40970696977777799</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.43331550933333302</v>
+        <v>0.39309581777777802</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.436880473777778</v>
+        <v>0.379304655111111</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.44391625244444399</v>
+        <v>0.40310519822222202</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.397660579555556</v>
+        <v>0.38591156799999998</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.43365957511111097</v>
+        <v>0.39334160533333301</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -511,7 +511,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.436312155911111</v>
+        <v>0.39263262497777796</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>1.5461663097504129E-2</v>
+        <v>1.2448522361985962E-2</v>
       </c>
     </row>
   </sheetData>
